--- a/excel/laddbox-kalkylator-data.xlsx
+++ b/excel/laddbox-kalkylator-data.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="124">
   <si>
     <t>model_id</t>
   </si>
@@ -134,49 +134,184 @@
     <t>price_sek</t>
   </si>
   <si>
+    <t>gross_price_sek</t>
+  </si>
+  <si>
+    <t>offert</t>
+  </si>
+  <si>
     <t>learn_more_url</t>
   </si>
   <si>
+    <t>zaptec-go</t>
+  </si>
+  <si>
+    <t>Zaptec Go</t>
+  </si>
+  <si>
+    <t>22 kW · inkl. installation</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+  <si>
+    <t>https://ampy.se/laddboxar/zaptec-go/</t>
+  </si>
+  <si>
+    <t>zaptec-go-2</t>
+  </si>
+  <si>
+    <t>Zaptec Go 2</t>
+  </si>
+  <si>
+    <t>https://ampy.se/laddboxar/zaptec-go-2/</t>
+  </si>
+  <si>
+    <t>easee-charge-up</t>
+  </si>
+  <si>
+    <t>Easee Charge Up</t>
+  </si>
+  <si>
+    <t>https://ampy.se/laddboxar/easee-charge-up/</t>
+  </si>
+  <si>
+    <t>nexblue-edge-2</t>
+  </si>
+  <si>
+    <t>NexBlue Edge 2</t>
+  </si>
+  <si>
+    <t>https://ampy.se/laddboxar/nexblue-edge-2/</t>
+  </si>
+  <si>
+    <t>go-e-gemini-flex-2-0</t>
+  </si>
+  <si>
+    <t>go-e Gemini Flex 2.0</t>
+  </si>
+  <si>
+    <t>https://ampy.se/laddboxar/go-e-gemini-flex-2-0/</t>
+  </si>
+  <si>
+    <t>tesla-wall-connector</t>
+  </si>
+  <si>
+    <t>Tesla Wall Connector</t>
+  </si>
+  <si>
+    <t>11 kW · inkl. installation</t>
+  </si>
+  <si>
+    <t>https://ampy.se/laddboxar/tesla-wall-connector/</t>
+  </si>
+  <si>
+    <t>charge-amps-luna</t>
+  </si>
+  <si>
+    <t>Charge Amps Luna</t>
+  </si>
+  <si>
+    <t>https://ampy.se/laddboxar/charge-amps-luna/</t>
+  </si>
+  <si>
+    <t>charge-amps-halo</t>
+  </si>
+  <si>
+    <t>Charge Amps Halo</t>
+  </si>
+  <si>
+    <t>https://ampy.se/laddboxar/charge-amps-halo/</t>
+  </si>
+  <si>
+    <t>charge-amps-dawn</t>
+  </si>
+  <si>
+    <t>Charge Amps Dawn</t>
+  </si>
+  <si>
+    <t>https://ampy.se/laddboxar/charge-amps-dawn/</t>
+  </si>
+  <si>
+    <t>charge-amps-aura</t>
+  </si>
+  <si>
+    <t>Charge Amps Aura</t>
+  </si>
+  <si>
+    <t>11 kW · stativ · inkl. installation</t>
+  </si>
+  <si>
+    <t>https://ampy.se/laddboxar/charge-amps-aura/</t>
+  </si>
+  <si>
+    <t>defa-power</t>
+  </si>
+  <si>
+    <t>Defa Power</t>
+  </si>
+  <si>
+    <t>https://ampy.se/laddboxar/defa-power/</t>
+  </si>
+  <si>
     <t>amina-s</t>
   </si>
   <si>
     <t>Amina S</t>
   </si>
   <si>
-    <t>Smart 11 kW · inkl. installation</t>
-  </si>
-  <si>
     <t>Rekommenderas</t>
   </si>
   <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>easee-charge</t>
-  </si>
-  <si>
-    <t>Easee Charge</t>
-  </si>
-  <si>
-    <t>Kompakt · inkl. installation</t>
-  </si>
-  <si>
-    <t>zaptec-go</t>
-  </si>
-  <si>
-    <t>Zaptec Go</t>
-  </si>
-  <si>
-    <t>Diskret · inkl. installation</t>
-  </si>
-  <si>
-    <t>garo-entity</t>
-  </si>
-  <si>
-    <t>Garo Entity</t>
-  </si>
-  <si>
-    <t>Svensktillverkad · inkl. installation</t>
+    <t>https://ampy.se/laddboxar/amina-s/</t>
+  </si>
+  <si>
+    <t>garo-entity-home</t>
+  </si>
+  <si>
+    <t>Garo Entity Home</t>
+  </si>
+  <si>
+    <t>https://ampy.se/laddboxar/garo-entity-home/</t>
+  </si>
+  <si>
+    <t>wallbox-pulsar-max</t>
+  </si>
+  <si>
+    <t>Wallbox Pulsar Max</t>
+  </si>
+  <si>
+    <t>https://ampy.se/laddboxar/wallbox-pulsar-max/</t>
+  </si>
+  <si>
+    <t>zaptec-pro</t>
+  </si>
+  <si>
+    <t>Zaptec Pro</t>
+  </si>
+  <si>
+    <t>För BRF &amp; företag · offert</t>
+  </si>
+  <si>
+    <t>Offert</t>
+  </si>
+  <si>
+    <t>https://ampy.se/laddboxar/zaptec-pro/</t>
+  </si>
+  <si>
+    <t>garo-entity-pro</t>
+  </si>
+  <si>
+    <t>Garo Entity Pro</t>
+  </si>
+  <si>
+    <t>För BRF &amp; företag</t>
+  </si>
+  <si>
+    <t>Företag/BRF</t>
+  </si>
+  <si>
+    <t>https://ampy.se/laddboxar/garo-entity-pro/</t>
   </si>
   <si>
     <t>area_code</t>
@@ -192,9 +327,6 @@
   </si>
   <si>
     <t>SE1 – Norra Sverige</t>
-  </si>
-  <si>
-    <t>false</t>
   </si>
   <si>
     <t>SE2</t>
@@ -826,10 +958,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>35</v>
       </c>
@@ -852,122 +984,536 @@
         <v>38</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F3">
-        <v>21900</v>
-      </c>
-      <c r="G3" t="s">
+        <v>4490</v>
+      </c>
+      <c r="G3">
+        <v>8980</v>
+      </c>
+      <c r="H3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4" t="s">
         <v>43</v>
-      </c>
-      <c r="H3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C4" t="s">
-        <v>46</v>
       </c>
       <c r="E4">
         <v>22</v>
       </c>
       <c r="F4">
-        <v>19900</v>
-      </c>
-      <c r="G4" t="s">
+        <v>5890</v>
+      </c>
+      <c r="G4">
+        <v>11780</v>
+      </c>
+      <c r="H4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I4" t="s">
+        <v>48</v>
+      </c>
+      <c r="J4" t="s">
+        <v>12</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" t="s">
         <v>43</v>
-      </c>
-      <c r="H4" t="s">
-        <v>12</v>
-      </c>
-      <c r="I4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" t="s">
-        <v>49</v>
       </c>
       <c r="E5">
         <v>22</v>
       </c>
       <c r="F5">
-        <v>20900</v>
-      </c>
-      <c r="G5" t="s">
+        <v>4390</v>
+      </c>
+      <c r="G5">
+        <v>8780</v>
+      </c>
+      <c r="H5" t="s">
+        <v>44</v>
+      </c>
+      <c r="I5" t="s">
+        <v>51</v>
+      </c>
+      <c r="J5" t="s">
+        <v>12</v>
+      </c>
+      <c r="K5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" t="s">
         <v>43</v>
-      </c>
-      <c r="H5" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" t="s">
-        <v>52</v>
       </c>
       <c r="E6">
         <v>22</v>
       </c>
       <c r="F6">
-        <v>22900</v>
-      </c>
-      <c r="G6" t="s">
+        <v>4190</v>
+      </c>
+      <c r="G6">
+        <v>8380</v>
+      </c>
+      <c r="H6" t="s">
+        <v>44</v>
+      </c>
+      <c r="I6" t="s">
+        <v>54</v>
+      </c>
+      <c r="J6" t="s">
+        <v>12</v>
+      </c>
+      <c r="K6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" t="s">
         <v>43</v>
       </c>
-      <c r="H6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I6">
-        <v>4</v>
+      <c r="E7">
+        <v>22</v>
+      </c>
+      <c r="F7">
+        <v>4990</v>
+      </c>
+      <c r="G7">
+        <v>9980</v>
+      </c>
+      <c r="H7" t="s">
+        <v>44</v>
+      </c>
+      <c r="I7" t="s">
+        <v>57</v>
+      </c>
+      <c r="J7" t="s">
+        <v>12</v>
+      </c>
+      <c r="K7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E8">
+        <v>11</v>
+      </c>
+      <c r="F8">
+        <v>4450</v>
+      </c>
+      <c r="G8">
+        <v>8900</v>
+      </c>
+      <c r="H8" t="s">
+        <v>44</v>
+      </c>
+      <c r="I8" t="s">
+        <v>61</v>
+      </c>
+      <c r="J8" t="s">
+        <v>12</v>
+      </c>
+      <c r="K8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9">
+        <v>22</v>
+      </c>
+      <c r="F9">
+        <v>4850</v>
+      </c>
+      <c r="G9">
+        <v>9700</v>
+      </c>
+      <c r="H9" t="s">
+        <v>44</v>
+      </c>
+      <c r="I9" t="s">
+        <v>64</v>
+      </c>
+      <c r="J9" t="s">
+        <v>12</v>
+      </c>
+      <c r="K9">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10">
+        <v>22</v>
+      </c>
+      <c r="F10">
+        <v>4990</v>
+      </c>
+      <c r="G10">
+        <v>9980</v>
+      </c>
+      <c r="H10" t="s">
+        <v>44</v>
+      </c>
+      <c r="I10" t="s">
+        <v>67</v>
+      </c>
+      <c r="J10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B11" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11">
+        <v>22</v>
+      </c>
+      <c r="F11">
+        <v>6850</v>
+      </c>
+      <c r="G11">
+        <v>13700</v>
+      </c>
+      <c r="H11" t="s">
+        <v>44</v>
+      </c>
+      <c r="I11" t="s">
+        <v>70</v>
+      </c>
+      <c r="J11" t="s">
+        <v>12</v>
+      </c>
+      <c r="K11">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>71</v>
+      </c>
+      <c r="B12" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" t="s">
+        <v>73</v>
+      </c>
+      <c r="E12">
+        <v>11</v>
+      </c>
+      <c r="F12">
+        <v>14550</v>
+      </c>
+      <c r="G12">
+        <v>29100</v>
+      </c>
+      <c r="H12" t="s">
+        <v>44</v>
+      </c>
+      <c r="I12" t="s">
+        <v>74</v>
+      </c>
+      <c r="J12" t="s">
+        <v>12</v>
+      </c>
+      <c r="K12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" t="s">
+        <v>75</v>
+      </c>
+      <c r="B13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13">
+        <v>22</v>
+      </c>
+      <c r="F13">
+        <v>5250</v>
+      </c>
+      <c r="G13">
+        <v>10500</v>
+      </c>
+      <c r="H13" t="s">
+        <v>44</v>
+      </c>
+      <c r="I13" t="s">
+        <v>77</v>
+      </c>
+      <c r="J13" t="s">
+        <v>12</v>
+      </c>
+      <c r="K13">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B14" t="s">
+        <v>79</v>
+      </c>
+      <c r="C14" t="s">
+        <v>60</v>
+      </c>
+      <c r="D14" t="s">
+        <v>80</v>
+      </c>
+      <c r="E14">
+        <v>11</v>
+      </c>
+      <c r="F14">
+        <v>4350</v>
+      </c>
+      <c r="G14">
+        <v>8700</v>
+      </c>
+      <c r="H14" t="s">
+        <v>44</v>
+      </c>
+      <c r="I14" t="s">
+        <v>81</v>
+      </c>
+      <c r="J14" t="s">
+        <v>12</v>
+      </c>
+      <c r="K14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>82</v>
+      </c>
+      <c r="B15" t="s">
+        <v>83</v>
+      </c>
+      <c r="C15" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15">
+        <v>22</v>
+      </c>
+      <c r="F15">
+        <v>5310</v>
+      </c>
+      <c r="G15">
+        <v>10620</v>
+      </c>
+      <c r="H15" t="s">
+        <v>44</v>
+      </c>
+      <c r="I15" t="s">
+        <v>84</v>
+      </c>
+      <c r="J15" t="s">
+        <v>12</v>
+      </c>
+      <c r="K15">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>85</v>
+      </c>
+      <c r="B16" t="s">
+        <v>86</v>
+      </c>
+      <c r="C16" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16">
+        <v>22</v>
+      </c>
+      <c r="F16">
+        <v>4425</v>
+      </c>
+      <c r="G16">
+        <v>8850</v>
+      </c>
+      <c r="H16" t="s">
+        <v>44</v>
+      </c>
+      <c r="I16" t="s">
+        <v>87</v>
+      </c>
+      <c r="J16" t="s">
+        <v>12</v>
+      </c>
+      <c r="K16">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>88</v>
+      </c>
+      <c r="B17" t="s">
+        <v>89</v>
+      </c>
+      <c r="C17" t="s">
+        <v>90</v>
+      </c>
+      <c r="D17" t="s">
+        <v>91</v>
+      </c>
+      <c r="E17">
+        <v>22</v>
+      </c>
+      <c r="H17" t="s">
+        <v>12</v>
+      </c>
+      <c r="I17" t="s">
+        <v>92</v>
+      </c>
+      <c r="J17" t="s">
+        <v>12</v>
+      </c>
+      <c r="K17">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>93</v>
+      </c>
+      <c r="B18" t="s">
+        <v>94</v>
+      </c>
+      <c r="C18" t="s">
+        <v>95</v>
+      </c>
+      <c r="D18" t="s">
+        <v>96</v>
+      </c>
+      <c r="E18">
+        <v>22</v>
+      </c>
+      <c r="F18">
+        <v>7350</v>
+      </c>
+      <c r="G18">
+        <v>14700</v>
+      </c>
+      <c r="H18" t="s">
+        <v>44</v>
+      </c>
+      <c r="I18" t="s">
+        <v>97</v>
+      </c>
+      <c r="J18" t="s">
+        <v>12</v>
+      </c>
+      <c r="K18">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -982,16 +1528,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>98</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>54</v>
+        <v>99</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>55</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1001,38 +1547,38 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>101</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="C3">
         <v>1.45</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>104</v>
       </c>
       <c r="C4">
         <v>1.5</v>
       </c>
       <c r="D4" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>105</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="C5">
         <v>1.9</v>
@@ -1043,16 +1589,16 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>63</v>
+        <v>107</v>
       </c>
       <c r="B6" t="s">
-        <v>64</v>
+        <v>108</v>
       </c>
       <c r="C6">
         <v>2.1</v>
       </c>
       <c r="D6" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -1067,10 +1613,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>109</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>66</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1080,7 +1626,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>67</v>
+        <v>111</v>
       </c>
       <c r="B3">
         <v>10</v>
@@ -1088,7 +1634,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>68</v>
+        <v>112</v>
       </c>
       <c r="B4">
         <v>4.5</v>
@@ -1096,7 +1642,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>69</v>
+        <v>113</v>
       </c>
       <c r="B5">
         <v>5.5</v>
@@ -1104,7 +1650,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>70</v>
+        <v>114</v>
       </c>
       <c r="B6">
         <v>0.9</v>
@@ -1112,7 +1658,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>71</v>
+        <v>115</v>
       </c>
       <c r="B7">
         <v>0.485</v>
@@ -1120,7 +1666,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>72</v>
+        <v>116</v>
       </c>
       <c r="B8">
         <v>50000</v>
@@ -1128,7 +1674,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="B9">
         <v>2</v>
@@ -1136,7 +1682,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>74</v>
+        <v>118</v>
       </c>
       <c r="B10">
         <v>0.1</v>
@@ -1154,10 +1700,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>109</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>75</v>
+        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1167,26 +1713,26 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>76</v>
+        <v>120</v>
       </c>
       <c r="B3">
-        <v>15000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>77</v>
+        <v>121</v>
       </c>
       <c r="B4">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>78</v>
+        <v>122</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>123</v>
       </c>
     </row>
   </sheetData>

--- a/excel/laddbox-kalkylator-data.xlsx
+++ b/excel/laddbox-kalkylator-data.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="139">
   <si>
     <t>model_id</t>
   </si>
@@ -149,7 +149,10 @@
     <t>Zaptec Go</t>
   </si>
   <si>
-    <t>22 kW · inkl. installation</t>
+    <t>Kompakt favorit · inkl. installation</t>
+  </si>
+  <si>
+    <t>Bästsäljare</t>
   </si>
   <si>
     <t>false</t>
@@ -164,6 +167,12 @@
     <t>Zaptec Go 2</t>
   </si>
   <si>
+    <t>Inbyggd display · inkl. installation</t>
+  </si>
+  <si>
+    <t>Rekommenderas</t>
+  </si>
+  <si>
     <t>https://ampy.se/laddboxar/zaptec-go-2/</t>
   </si>
   <si>
@@ -173,6 +182,9 @@
     <t>Easee Charge Up</t>
   </si>
   <si>
+    <t>Smart &amp; nätt · inkl. installation</t>
+  </si>
+  <si>
     <t>https://ampy.se/laddboxar/easee-charge-up/</t>
   </si>
   <si>
@@ -182,6 +194,12 @@
     <t>NexBlue Edge 2</t>
   </si>
   <si>
+    <t>Prisbelönt design · inkl. installation</t>
+  </si>
+  <si>
+    <t>Prisvärd</t>
+  </si>
+  <si>
     <t>https://ampy.se/laddboxar/nexblue-edge-2/</t>
   </si>
   <si>
@@ -191,6 +209,9 @@
     <t>go-e Gemini Flex 2.0</t>
   </si>
   <si>
+    <t>Fast eller flyttbar · inkl. installation</t>
+  </si>
+  <si>
     <t>https://ampy.se/laddboxar/go-e-gemini-flex-2-0/</t>
   </si>
   <si>
@@ -200,7 +221,7 @@
     <t>Tesla Wall Connector</t>
   </si>
   <si>
-    <t>11 kW · inkl. installation</t>
+    <t>Fast kabel 7,3 m · inkl. installation</t>
   </si>
   <si>
     <t>https://ampy.se/laddboxar/tesla-wall-connector/</t>
@@ -212,6 +233,9 @@
     <t>Charge Amps Luna</t>
   </si>
   <si>
+    <t>Skandinavisk design · inkl. installation</t>
+  </si>
+  <si>
     <t>https://ampy.se/laddboxar/charge-amps-luna/</t>
   </si>
   <si>
@@ -221,6 +245,9 @@
     <t>Charge Amps Halo</t>
   </si>
   <si>
+    <t>Fast kabel &amp; statusljus · inkl. installation</t>
+  </si>
+  <si>
     <t>https://ampy.se/laddboxar/charge-amps-halo/</t>
   </si>
   <si>
@@ -230,6 +257,9 @@
     <t>Charge Amps Dawn</t>
   </si>
   <si>
+    <t>Svensktillverkad premium · inkl. installation</t>
+  </si>
+  <si>
     <t>https://ampy.se/laddboxar/charge-amps-dawn/</t>
   </si>
   <si>
@@ -239,7 +269,10 @@
     <t>Charge Amps Aura</t>
   </si>
   <si>
-    <t>11 kW · stativ · inkl. installation</t>
+    <t>Två bilar samtidigt · inkl. installation</t>
+  </si>
+  <si>
+    <t>Dubbel laddning</t>
   </si>
   <si>
     <t>https://ampy.se/laddboxar/charge-amps-aura/</t>
@@ -251,6 +284,9 @@
     <t>Defa Power</t>
   </si>
   <si>
+    <t>Display &amp; −40 °C · inkl. installation</t>
+  </si>
+  <si>
     <t>https://ampy.se/laddboxar/defa-power/</t>
   </si>
   <si>
@@ -260,7 +296,7 @@
     <t>Amina S</t>
   </si>
   <si>
-    <t>Rekommenderas</t>
+    <t>Marknadens minsta · inkl. installation</t>
   </si>
   <si>
     <t>https://ampy.se/laddboxar/amina-s/</t>
@@ -272,6 +308,9 @@
     <t>Garo Entity Home</t>
   </si>
   <si>
+    <t>Driftsäker villabox · inkl. installation</t>
+  </si>
+  <si>
     <t>https://ampy.se/laddboxar/garo-entity-home/</t>
   </si>
   <si>
@@ -281,6 +320,9 @@
     <t>Wallbox Pulsar Max</t>
   </si>
   <si>
+    <t>Prisbelönt &amp; kompakt · inkl. installation</t>
+  </si>
+  <si>
     <t>https://ampy.se/laddboxar/wallbox-pulsar-max/</t>
   </si>
   <si>
@@ -290,7 +332,7 @@
     <t>Zaptec Pro</t>
   </si>
   <si>
-    <t>För BRF &amp; företag · offert</t>
+    <t>Skalbar för flera platser · offert</t>
   </si>
   <si>
     <t>Offert</t>
@@ -305,7 +347,7 @@
     <t>Garo Entity Pro</t>
   </si>
   <si>
-    <t>För BRF &amp; företag</t>
+    <t>Byggd för många bilar</t>
   </si>
   <si>
     <t>Företag/BRF</t>
@@ -318,6 +360,9 @@
   </si>
   <si>
     <t>home_rate_sek_per_kwh</t>
+  </si>
+  <si>
+    <t>home_rate_optimized_sek_per_kwh</t>
   </si>
   <si>
     <t>is_default</t>
@@ -1011,6 +1056,9 @@
       <c r="C3" t="s">
         <v>43</v>
       </c>
+      <c r="D3" t="s">
+        <v>44</v>
+      </c>
       <c r="E3">
         <v>22</v>
       </c>
@@ -1021,10 +1069,10 @@
         <v>8980</v>
       </c>
       <c r="H3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J3" t="s">
         <v>12</v>
@@ -1035,13 +1083,16 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>49</v>
+      </c>
+      <c r="D4" t="s">
+        <v>50</v>
       </c>
       <c r="E4">
         <v>22</v>
@@ -1053,10 +1104,10 @@
         <v>11780</v>
       </c>
       <c r="H4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J4" t="s">
         <v>12</v>
@@ -1067,13 +1118,16 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>54</v>
+      </c>
+      <c r="D5" t="s">
+        <v>44</v>
       </c>
       <c r="E5">
         <v>22</v>
@@ -1085,10 +1139,10 @@
         <v>8780</v>
       </c>
       <c r="H5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I5" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="J5" t="s">
         <v>12</v>
@@ -1099,13 +1153,16 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C6" t="s">
-        <v>43</v>
+        <v>58</v>
+      </c>
+      <c r="D6" t="s">
+        <v>59</v>
       </c>
       <c r="E6">
         <v>22</v>
@@ -1117,10 +1174,10 @@
         <v>8380</v>
       </c>
       <c r="H6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I6" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="J6" t="s">
         <v>12</v>
@@ -1131,13 +1188,13 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="E7">
         <v>22</v>
@@ -1149,10 +1206,10 @@
         <v>9980</v>
       </c>
       <c r="H7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I7" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="J7" t="s">
         <v>12</v>
@@ -1163,13 +1220,13 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C8" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="E8">
         <v>11</v>
@@ -1181,10 +1238,10 @@
         <v>8900</v>
       </c>
       <c r="H8" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I8" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J8" t="s">
         <v>12</v>
@@ -1195,13 +1252,13 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="E9">
         <v>22</v>
@@ -1213,10 +1270,10 @@
         <v>9700</v>
       </c>
       <c r="H9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I9" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="J9" t="s">
         <v>12</v>
@@ -1227,13 +1284,13 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="E10">
         <v>22</v>
@@ -1245,10 +1302,10 @@
         <v>9980</v>
       </c>
       <c r="H10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I10" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="J10" t="s">
         <v>12</v>
@@ -1259,13 +1316,13 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="E11">
         <v>22</v>
@@ -1277,10 +1334,10 @@
         <v>13700</v>
       </c>
       <c r="H11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I11" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="J11" t="s">
         <v>12</v>
@@ -1291,16 +1348,19 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="B12" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="C12" t="s">
-        <v>73</v>
+        <v>83</v>
+      </c>
+      <c r="D12" t="s">
+        <v>84</v>
       </c>
       <c r="E12">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F12">
         <v>14550</v>
@@ -1309,10 +1369,10 @@
         <v>29100</v>
       </c>
       <c r="H12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I12" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="J12" t="s">
         <v>12</v>
@@ -1323,13 +1383,13 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="C13" t="s">
-        <v>43</v>
+        <v>88</v>
       </c>
       <c r="E13">
         <v>22</v>
@@ -1341,10 +1401,10 @@
         <v>10500</v>
       </c>
       <c r="H13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I13" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J13" t="s">
         <v>12</v>
@@ -1355,16 +1415,13 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="B14" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="C14" t="s">
-        <v>60</v>
-      </c>
-      <c r="D14" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="E14">
         <v>11</v>
@@ -1376,10 +1433,10 @@
         <v>8700</v>
       </c>
       <c r="H14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I14" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="J14" t="s">
         <v>12</v>
@@ -1390,13 +1447,13 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="B15" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="C15" t="s">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="E15">
         <v>22</v>
@@ -1408,10 +1465,10 @@
         <v>10620</v>
       </c>
       <c r="H15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I15" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="J15" t="s">
         <v>12</v>
@@ -1422,13 +1479,13 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="B16" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="C16" t="s">
-        <v>43</v>
+        <v>100</v>
       </c>
       <c r="E16">
         <v>22</v>
@@ -1440,10 +1497,10 @@
         <v>8850</v>
       </c>
       <c r="H16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I16" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="J16" t="s">
         <v>12</v>
@@ -1454,16 +1511,16 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="B17" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="C17" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="D17" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="E17">
         <v>22</v>
@@ -1472,7 +1529,7 @@
         <v>12</v>
       </c>
       <c r="I17" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="J17" t="s">
         <v>12</v>
@@ -1483,16 +1540,16 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="B18" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="C18" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="D18" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="E18">
         <v>22</v>
@@ -1504,10 +1561,10 @@
         <v>14700</v>
       </c>
       <c r="H18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I18" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="J18" t="s">
         <v>12</v>
@@ -1523,82 +1580,97 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+        <v>114</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="B3" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="C3">
         <v>1.45</v>
       </c>
-      <c r="D3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="D3">
+        <v>1.05</v>
+      </c>
+      <c r="E3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="B4" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="C4">
         <v>1.5</v>
       </c>
-      <c r="D4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="D4">
+        <v>1.15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="B5" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="C5">
         <v>1.9</v>
       </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="D5">
+        <v>1.35</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="B6" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="C6">
         <v>2.1</v>
       </c>
-      <c r="D6" t="s">
-        <v>44</v>
+      <c r="D6">
+        <v>1.45</v>
+      </c>
+      <c r="E6" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1613,10 +1685,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1626,7 +1698,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="B3">
         <v>10</v>
@@ -1634,7 +1706,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="B4">
         <v>4.5</v>
@@ -1642,7 +1714,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="B5">
         <v>5.5</v>
@@ -1650,7 +1722,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="B6">
         <v>0.9</v>
@@ -1658,7 +1730,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="B7">
         <v>0.485</v>
@@ -1666,7 +1738,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="B8">
         <v>50000</v>
@@ -1674,7 +1746,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="B9">
         <v>2</v>
@@ -1682,7 +1754,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="B10">
         <v>0.1</v>
@@ -1700,10 +1772,10 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1713,7 +1785,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="B3">
         <v>20000</v>
@@ -1721,7 +1793,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="B4">
         <v>100</v>
@@ -1729,10 +1801,10 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="B5" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>

--- a/excel/laddbox-kalkylator-data.xlsx
+++ b/excel/laddbox-kalkylator-data.xlsx
@@ -149,7 +149,7 @@
     <t>Zaptec Go</t>
   </si>
   <si>
-    <t>Kompakt favorit · inkl. installation</t>
+    <t>Kompakt favorit</t>
   </si>
   <si>
     <t>Bästsäljare</t>
@@ -167,7 +167,7 @@
     <t>Zaptec Go 2</t>
   </si>
   <si>
-    <t>Inbyggd display · inkl. installation</t>
+    <t>Inbyggd display</t>
   </si>
   <si>
     <t>Rekommenderas</t>
@@ -182,7 +182,7 @@
     <t>Easee Charge Up</t>
   </si>
   <si>
-    <t>Smart &amp; nätt · inkl. installation</t>
+    <t>Smart &amp; nätt</t>
   </si>
   <si>
     <t>https://ampy.se/laddboxar/easee-charge-up/</t>
@@ -194,7 +194,7 @@
     <t>NexBlue Edge 2</t>
   </si>
   <si>
-    <t>Prisbelönt design · inkl. installation</t>
+    <t>Prisbelönt design</t>
   </si>
   <si>
     <t>Prisvärd</t>
@@ -209,7 +209,7 @@
     <t>go-e Gemini Flex 2.0</t>
   </si>
   <si>
-    <t>Fast eller flyttbar · inkl. installation</t>
+    <t>Fast eller flyttbar</t>
   </si>
   <si>
     <t>https://ampy.se/laddboxar/go-e-gemini-flex-2-0/</t>
@@ -221,7 +221,7 @@
     <t>Tesla Wall Connector</t>
   </si>
   <si>
-    <t>Fast kabel 7,3 m · inkl. installation</t>
+    <t>Fast kabel 7,3 m</t>
   </si>
   <si>
     <t>https://ampy.se/laddboxar/tesla-wall-connector/</t>
@@ -233,7 +233,7 @@
     <t>Charge Amps Luna</t>
   </si>
   <si>
-    <t>Skandinavisk design · inkl. installation</t>
+    <t>Skandinavisk design</t>
   </si>
   <si>
     <t>https://ampy.se/laddboxar/charge-amps-luna/</t>
@@ -245,7 +245,7 @@
     <t>Charge Amps Halo</t>
   </si>
   <si>
-    <t>Fast kabel &amp; statusljus · inkl. installation</t>
+    <t>Fast kabel &amp; statusljus</t>
   </si>
   <si>
     <t>https://ampy.se/laddboxar/charge-amps-halo/</t>
@@ -257,7 +257,7 @@
     <t>Charge Amps Dawn</t>
   </si>
   <si>
-    <t>Svensktillverkad premium · inkl. installation</t>
+    <t>Svensktillverkad premium</t>
   </si>
   <si>
     <t>https://ampy.se/laddboxar/charge-amps-dawn/</t>
@@ -269,7 +269,7 @@
     <t>Charge Amps Aura</t>
   </si>
   <si>
-    <t>Två bilar samtidigt · inkl. installation</t>
+    <t>Två bilar samtidigt</t>
   </si>
   <si>
     <t>Dubbel laddning</t>
@@ -284,7 +284,7 @@
     <t>Defa Power</t>
   </si>
   <si>
-    <t>Display &amp; −40 °C · inkl. installation</t>
+    <t>Display &amp; −40 °C</t>
   </si>
   <si>
     <t>https://ampy.se/laddboxar/defa-power/</t>
@@ -296,7 +296,7 @@
     <t>Amina S</t>
   </si>
   <si>
-    <t>Marknadens minsta · inkl. installation</t>
+    <t>Marknadens minsta</t>
   </si>
   <si>
     <t>https://ampy.se/laddboxar/amina-s/</t>
@@ -308,7 +308,7 @@
     <t>Garo Entity Home</t>
   </si>
   <si>
-    <t>Driftsäker villabox · inkl. installation</t>
+    <t>Driftsäker villabox</t>
   </si>
   <si>
     <t>https://ampy.se/laddboxar/garo-entity-home/</t>
@@ -320,7 +320,7 @@
     <t>Wallbox Pulsar Max</t>
   </si>
   <si>
-    <t>Prisbelönt &amp; kompakt · inkl. installation</t>
+    <t>Prisbelönt &amp; kompakt</t>
   </si>
   <si>
     <t>https://ampy.se/laddboxar/wallbox-pulsar-max/</t>
@@ -1613,10 +1613,10 @@
         <v>117</v>
       </c>
       <c r="C3">
-        <v>1.45</v>
+        <v>1.1</v>
       </c>
       <c r="D3">
-        <v>1.05</v>
+        <v>0.6</v>
       </c>
       <c r="E3" t="s">
         <v>45</v>
@@ -1630,10 +1630,10 @@
         <v>119</v>
       </c>
       <c r="C4">
-        <v>1.5</v>
+        <v>1.15</v>
       </c>
       <c r="D4">
-        <v>1.15</v>
+        <v>0.65</v>
       </c>
       <c r="E4" t="s">
         <v>45</v>
@@ -1647,10 +1647,10 @@
         <v>121</v>
       </c>
       <c r="C5">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="D5">
-        <v>1.35</v>
+        <v>0.9</v>
       </c>
       <c r="E5" t="s">
         <v>12</v>
@@ -1664,10 +1664,10 @@
         <v>123</v>
       </c>
       <c r="C6">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="D6">
-        <v>1.45</v>
+        <v>1</v>
       </c>
       <c r="E6" t="s">
         <v>45</v>

--- a/excel/laddbox-kalkylator-data.xlsx
+++ b/excel/laddbox-kalkylator-data.xlsx
@@ -149,7 +149,7 @@
     <t>Zaptec Go</t>
   </si>
   <si>
-    <t>Kompakt favorit</t>
+    <t>Kompakt, upp till 22 kW</t>
   </si>
   <si>
     <t>Bästsäljare</t>
@@ -167,7 +167,7 @@
     <t>Zaptec Go 2</t>
   </si>
   <si>
-    <t>Inbyggd display</t>
+    <t>Nu med inbyggd skärm</t>
   </si>
   <si>
     <t>Rekommenderas</t>
@@ -182,7 +182,7 @@
     <t>Easee Charge Up</t>
   </si>
   <si>
-    <t>Smart &amp; nätt</t>
+    <t>Smart laddning via app</t>
   </si>
   <si>
     <t>https://ampy.se/laddboxar/easee-charge-up/</t>
@@ -221,7 +221,7 @@
     <t>Tesla Wall Connector</t>
   </si>
   <si>
-    <t>Fast kabel 7,3 m</t>
+    <t>Fast kabel, 7,3 m</t>
   </si>
   <si>
     <t>https://ampy.se/laddboxar/tesla-wall-connector/</t>
@@ -284,7 +284,7 @@
     <t>Defa Power</t>
   </si>
   <si>
-    <t>Display &amp; −40 °C</t>
+    <t>Display, klarar −40 °C</t>
   </si>
   <si>
     <t>https://ampy.se/laddboxar/defa-power/</t>
@@ -332,7 +332,7 @@
     <t>Zaptec Pro</t>
   </si>
   <si>
-    <t>Skalbar för flera platser · offert</t>
+    <t>Skalbar för flera platser</t>
   </si>
   <si>
     <t>Offert</t>
